--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260616.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260616.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>162,925</t>
+          <t>160,425</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>26.98%</t>
+          <t>26.31%</t>
         </is>
       </c>
     </row>
@@ -633,56 +633,56 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>118,130</t>
+          <t>116,360</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.57%</t>
+          <t>9.54%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>MRVL US</t>
+          <t>GEV US</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Marvell Technology Inc</t>
+          <t>奇異維諾瓦公司</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>60,105</t>
+          <t>18,295</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.81%</t>
+          <t>7.82%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>GEV US</t>
+          <t>MRVL US</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>奇異維諾瓦公司</t>
+          <t>Marvell Technology Inc</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>18,575</t>
+          <t>59,235</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.65%</t>
+          <t>7.19%</t>
         </is>
       </c>
     </row>
@@ -699,34 +699,34 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>143,395</t>
+          <t>141,245</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.19%</t>
+          <t>5.30%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>NOW US</t>
+          <t>EQIX US</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>ServiceNow Inc</t>
+          <t>Equinix公司</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>70,230</t>
+          <t>6,665</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>3.18%</t>
         </is>
       </c>
     </row>
@@ -743,34 +743,34 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>77,365</t>
+          <t>76,205</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.05%</t>
+          <t>3.13%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>EQIX US</t>
+          <t>NOW US</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Equinix公司</t>
+          <t>ServiceNow Inc</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>6,765</t>
+          <t>69,180</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>3.05%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>53,355</t>
+          <t>52,555</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.81%</t>
+          <t>2.88%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>23,335</t>
+          <t>22,985</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>2.68%</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>21,583</t>
+          <t>21,263</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -853,56 +853,56 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>37,250</t>
+          <t>36,690</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>2.07%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>HPE US</t>
+          <t>DLR US</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>慧與</t>
+          <t>數位不動產信託公司</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>90,915</t>
+          <t>23,595</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.96%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>DLR US</t>
+          <t>HPE US</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>數位不動產信託公司</t>
+          <t>慧與</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>23,955</t>
+          <t>89,555</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>1.89%</t>
         </is>
       </c>
     </row>
@@ -919,34 +919,34 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>60,305</t>
+          <t>59,405</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.77%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>9,440</t>
+          <t>22,690</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.57%</t>
         </is>
       </c>
     </row>
@@ -963,51 +963,51 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>13,831</t>
+          <t>13,631</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.57%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>23,040</t>
+          <t>30,928</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.51%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>31,398</t>
+          <t>9,310</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>42,800</t>
+          <t>42,160</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.45%</t>
         </is>
       </c>
     </row>
@@ -1051,56 +1051,56 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>70,208</t>
+          <t>69,158</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.40%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>ED US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>聯合愛迪生</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>11,376</t>
+          <t>24,848</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.17%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>ED US</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>聯合愛迪生</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>25,228</t>
+          <t>11,206</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.17%</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>23,307</t>
+          <t>22,957</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.17%</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>21,865</t>
+          <t>21,535</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.08%</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>149,895</t>
+          <t>147,645</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.08%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>18,871</t>
+          <t>18,591</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>44,340</t>
+          <t>43,670</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>51,070</t>
+          <t>50,300</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>14,015</t>
+          <t>13,765</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.68%</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,56 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>1,303,597</t>
+          <t>1,399,555</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.61%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>RDI_NTD</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>94,695,000</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>RDI_USD</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>3,481,767</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
